--- a/Project status.xlsx
+++ b/Project status.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-20.04\home\shazad\Project2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9EB547C-70F6-4560-B14B-924D9E144D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034A28EF-C499-4770-AE75-2E0577FA1765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{1604AB3E-B7A5-48B8-8DF5-9AA376601063}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="46">
   <si>
     <t>Sr no</t>
   </si>
@@ -59,9 +60,6 @@
     <t>https://www.youtube.com/watch?v=QlbyGPVaRSE</t>
   </si>
   <si>
-    <t>Learning_goal_EDA.txt</t>
-  </si>
-  <si>
     <t>Data</t>
   </si>
   <si>
@@ -138,11 +136,6 @@
   </si>
   <si>
     <t>https://www.kaggle.com/code/lalina/exploratory-data-analysis-project/input</t>
-  </si>
-  <si>
-    <t>Prompt Learning Goals + Reasoning: For given topic : #topic name
-What all should be my learning Goals, please list them.
-I am a Professional Machine Learning Engineer.</t>
   </si>
   <si>
     <t>https://www.geeksforgeeks.org/data-analysis-tutorial/?ref=
@@ -156,13 +149,40 @@
   </si>
   <si>
     <t>Practical Completed</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>https://scikit-learn.org/1.4/auto_examples/datasets/plot_iris_dataset.html</t>
+  </si>
+  <si>
+    <t>https://eminebozkus.medium.com/exploring-the-iris-flower-dataset-4e000bcc266c</t>
+  </si>
+  <si>
+    <t>Learning Goals\EDA.html</t>
+  </si>
+  <si>
+    <t>Learning Goals\IrisFlower.html</t>
+  </si>
+  <si>
+    <t>Revision Date</t>
+  </si>
+  <si>
+    <t>13/4/25</t>
+  </si>
+  <si>
+    <t>20/4/25</t>
+  </si>
+  <si>
+    <t>LO started</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,8 +231,29 @@
       <name val="Arial Unicode MS"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -223,6 +264,21 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -250,30 +306,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -283,12 +333,79 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="5">
+    <cellStyle name="Bad" xfId="3" builtinId="27"/>
+    <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Neutral" xfId="4" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -679,29 +796,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EC30A07-1E56-4DE9-B93A-7590D850F4A2}">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="48.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.28515625" customWidth="1"/>
-    <col min="6" max="7" width="30" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.7109375" style="12" customWidth="1"/>
+    <col min="6" max="6" width="41.28515625" style="12" customWidth="1"/>
+    <col min="7" max="7" width="19" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -709,447 +828,544 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G4" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>5</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
         <v>8</v>
       </c>
-      <c r="G3" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="B11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
         <v>9</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>2</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="B12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
         <v>10</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="9"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>3</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="B13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
         <v>11</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="9"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>4</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="B14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
         <v>12</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="9"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>5</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="B15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
         <v>13</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>6</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="B16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
         <v>14</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>7</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="B17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
         <v>15</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <v>8</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="B18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
         <v>16</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <v>9</v>
-      </c>
-      <c r="B12" s="4" t="s">
+      <c r="B19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
         <v>17</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <v>10</v>
-      </c>
-      <c r="B13" s="4" t="s">
+      <c r="B20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
         <v>18</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
-        <v>11</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="B21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
         <v>19</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <v>12</v>
-      </c>
-      <c r="B15" s="4" t="s">
+      <c r="B22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
         <v>20</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <v>13</v>
-      </c>
-      <c r="B16" s="4" t="s">
+      <c r="B23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
         <v>21</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
-        <v>14</v>
-      </c>
-      <c r="B17" s="4" t="s">
+      <c r="B24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="3"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
         <v>22</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
-        <v>15</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
-        <v>16</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
-        <v>17</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
-        <v>18</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
-        <v>19</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
-        <v>20</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
-        <v>21</v>
-      </c>
-      <c r="B24" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
-        <v>22</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-    </row>
-    <row r="30" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
-      <c r="F30" s="3" t="str">
+      <c r="C25" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F30" s="18" t="str">
         <f>SUBSTITUTE(B26, "* ", "")</f>
         <v/>
       </c>
-      <c r="G30" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F31" s="3" t="str">
+      <c r="G30" s="6"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F31" s="18" t="str">
         <f>SUBSTITUTE(B27, "* ", "")</f>
         <v/>
       </c>
-      <c r="G31" s="3"/>
+      <c r="G31" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
       <formula>"Started"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K4:K5">
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"Started"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K6">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{71DC694D-6B6C-4B09-A580-03BE6BAB9B82}"/>
+    <hyperlink ref="E4" r:id="rId2" display="https://www.kaggle.com/code/lalina/exploratory-data-analysis-project" xr:uid="{16E90A10-6B1F-4CEC-A84A-8F18DD596599}"/>
+    <hyperlink ref="F4" r:id="rId3" xr:uid="{CA40A01B-0BB1-4CAC-82B6-677133F4EAA6}"/>
+    <hyperlink ref="B1" r:id="rId4" location="gid=0" xr:uid="{529FB104-2BCC-4371-BD01-98284FFD6048}"/>
+    <hyperlink ref="F5" r:id="rId5" xr:uid="{A878AB21-4F27-4AB4-AA67-D57115AF88E6}"/>
+    <hyperlink ref="E5" r:id="rId6" xr:uid="{FE1A3EBB-00C8-4C67-AE93-4688816BF19B}"/>
+    <hyperlink ref="D4" r:id="rId7" xr:uid="{3795AD77-DC0D-40A7-9286-4E7211A3D863}"/>
+    <hyperlink ref="D5" r:id="rId8" xr:uid="{A19F5BE6-4058-40D2-A3F7-8D820AB478A1}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DAC23794-297F-4325-8D1F-D24731B701DB}">
+          <x14:formula1>
+            <xm:f>Sheet2!$A$2:$A$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>C4:C25</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{066E3D44-C043-4A78-A289-932BB6DD4A7A}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3"/>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"Completed"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>"In Progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+      <formula>"Not Started"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+      <formula>"Started"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4:C25" xr:uid="{DAC23794-297F-4325-8D1F-D24731B701DB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1" xr:uid="{4D2E01C0-62EF-45CA-BD4B-AFB0DA1ECE2C}">
       <formula1>$K$4:$K$6</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" xr:uid="{E5A5BBD3-9DF1-4AB1-81F9-672E3B20A018}"/>
-    <hyperlink ref="B2" r:id="rId2" xr:uid="{71DC694D-6B6C-4B09-A580-03BE6BAB9B82}"/>
-    <hyperlink ref="E4" r:id="rId3" display="https://www.kaggle.com/code/lalina/exploratory-data-analysis-project" xr:uid="{16E90A10-6B1F-4CEC-A84A-8F18DD596599}"/>
-    <hyperlink ref="F4" r:id="rId4" xr:uid="{CA40A01B-0BB1-4CAC-82B6-677133F4EAA6}"/>
-    <hyperlink ref="B1" r:id="rId5" location="gid=0" xr:uid="{529FB104-2BCC-4371-BD01-98284FFD6048}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Project status.xlsx
+++ b/Project status.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-20.04\home\shazad\Project2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034A28EF-C499-4770-AE75-2E0577FA1765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8915C3AA-FBA6-4EE8-A195-1A4D0F6B6F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{1604AB3E-B7A5-48B8-8DF5-9AA376601063}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="42">
   <si>
     <t>Sr no</t>
   </si>
@@ -60,6 +60,9 @@
     <t>https://www.youtube.com/watch?v=QlbyGPVaRSE</t>
   </si>
   <si>
+    <t>Learning_goal_EDA.txt</t>
+  </si>
+  <si>
     <t>Data</t>
   </si>
   <si>
@@ -136,6 +139,11 @@
   </si>
   <si>
     <t>https://www.kaggle.com/code/lalina/exploratory-data-analysis-project/input</t>
+  </si>
+  <si>
+    <t>Prompt Learning Goals + Reasoning: For given topic : #topic name
+What all should be my learning Goals, please list them.
+I am a Professional Machine Learning Engineer.</t>
   </si>
   <si>
     <t>https://www.geeksforgeeks.org/data-analysis-tutorial/?ref=
@@ -148,41 +156,23 @@
     <t xml:space="preserve">Question: </t>
   </si>
   <si>
-    <t>Practical Completed</t>
-  </si>
-  <si>
     <t>Completed</t>
   </si>
   <si>
-    <t>https://scikit-learn.org/1.4/auto_examples/datasets/plot_iris_dataset.html</t>
-  </si>
-  <si>
-    <t>https://eminebozkus.medium.com/exploring-the-iris-flower-dataset-4e000bcc266c</t>
-  </si>
-  <si>
-    <t>Learning Goals\EDA.html</t>
-  </si>
-  <si>
-    <t>Learning Goals\IrisFlower.html</t>
-  </si>
-  <si>
-    <t>Revision Date</t>
-  </si>
-  <si>
-    <t>13/4/25</t>
-  </si>
-  <si>
-    <t>20/4/25</t>
-  </si>
-  <si>
-    <t>LO started</t>
+    <t>Planned start date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panned End date </t>
+  </si>
+  <si>
+    <t>YTS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,29 +221,8 @@
       <name val="Arial Unicode MS"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -268,17 +237,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -306,66 +266,89 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="5">
-    <cellStyle name="Bad" xfId="3" builtinId="27"/>
-    <cellStyle name="Good" xfId="2" builtinId="26"/>
+  <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Neutral" xfId="4" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -796,31 +779,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EC30A07-1E56-4DE9-B93A-7590D850F4A2}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="48.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="44.7109375" style="12" customWidth="1"/>
-    <col min="6" max="6" width="41.28515625" style="12" customWidth="1"/>
-    <col min="7" max="7" width="19" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.28515625" customWidth="1"/>
+    <col min="6" max="9" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -828,481 +809,507 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="D4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="E4" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="15">
+        <v>45812</v>
+      </c>
+      <c r="H4" s="15">
+        <v>45815</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>2</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>1</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="B5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="9"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>3</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="9"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="9"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>5</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>6</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>7</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
         <v>8</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>2</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="B11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
         <v>9</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>3</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="B12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
         <v>10</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="B13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>11</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>12</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>13</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>14</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>15</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>16</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>17</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>18</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>19</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <v>20</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <v>21</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>22</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <v>5</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
-        <v>6</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
-        <v>7</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <v>8</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>9</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
-        <v>10</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
-        <v>11</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="3"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>12</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="3"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <v>13</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <v>14</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="3"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
-        <v>15</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
-        <v>16</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
-        <v>17</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
-        <v>18</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
-        <v>19</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
-        <v>20</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
-        <v>21</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="3"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
-        <v>22</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="3"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F30" s="18" t="str">
+      <c r="C25" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+    </row>
+    <row r="30" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="F30" s="3" t="str">
         <f>SUBSTITUTE(B26, "* ", "")</f>
         <v/>
       </c>
-      <c r="G30" s="6"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F31" s="18" t="str">
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F31" s="3" t="str">
         <f>SUBSTITUTE(B27, "* ", "")</f>
         <v/>
       </c>
-      <c r="G31" s="18"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="C4:C25">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="9" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="10" operator="equal">
       <formula>"Started"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="equal">
+  <conditionalFormatting sqref="M4">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:K5">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
+  <conditionalFormatting sqref="M4:M5">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
       <formula>"Started"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6">
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+  <conditionalFormatting sqref="M6">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{71DC694D-6B6C-4B09-A580-03BE6BAB9B82}"/>
-    <hyperlink ref="E4" r:id="rId2" display="https://www.kaggle.com/code/lalina/exploratory-data-analysis-project" xr:uid="{16E90A10-6B1F-4CEC-A84A-8F18DD596599}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{CA40A01B-0BB1-4CAC-82B6-677133F4EAA6}"/>
-    <hyperlink ref="B1" r:id="rId4" location="gid=0" xr:uid="{529FB104-2BCC-4371-BD01-98284FFD6048}"/>
-    <hyperlink ref="F5" r:id="rId5" xr:uid="{A878AB21-4F27-4AB4-AA67-D57115AF88E6}"/>
-    <hyperlink ref="E5" r:id="rId6" xr:uid="{FE1A3EBB-00C8-4C67-AE93-4688816BF19B}"/>
-    <hyperlink ref="D4" r:id="rId7" xr:uid="{3795AD77-DC0D-40A7-9286-4E7211A3D863}"/>
-    <hyperlink ref="D5" r:id="rId8" xr:uid="{A19F5BE6-4058-40D2-A3F7-8D820AB478A1}"/>
+    <hyperlink ref="D4" r:id="rId1" xr:uid="{E5A5BBD3-9DF1-4AB1-81F9-672E3B20A018}"/>
+    <hyperlink ref="B2" r:id="rId2" xr:uid="{71DC694D-6B6C-4B09-A580-03BE6BAB9B82}"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://www.kaggle.com/code/lalina/exploratory-data-analysis-project" xr:uid="{16E90A10-6B1F-4CEC-A84A-8F18DD596599}"/>
+    <hyperlink ref="F4" r:id="rId4" xr:uid="{CA40A01B-0BB1-4CAC-82B6-677133F4EAA6}"/>
+    <hyperlink ref="B1" r:id="rId5" location="gid=0" xr:uid="{529FB104-2BCC-4371-BD01-98284FFD6048}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
@@ -1321,33 +1328,44 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{066E3D44-C043-4A78-A289-932BB6DD4A7A}">
-  <dimension ref="A1:A4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D10F673-2C90-4444-AE5C-BA03147A7D83}">
+  <dimension ref="A2:A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3"/>
-    </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>30</v>
+      <c r="A2" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>3</v>
+      <c r="A3" s="13" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>37</v>
+      <c r="A4" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1">
+  <conditionalFormatting sqref="A2">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+      <formula>"Completed"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+      <formula>"In Progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+      <formula>"Not Started"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="8" operator="equal">
+      <formula>"Started"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"Completed"</formula>
     </cfRule>
@@ -1362,8 +1380,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1" xr:uid="{4D2E01C0-62EF-45CA-BD4B-AFB0DA1ECE2C}">
-      <formula1>$K$4:$K$6</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2 A4" xr:uid="{B87B3083-DD60-46AE-A8EC-8BD3E696B9E5}">
+      <formula1>$N$4:$N$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
